--- a/Sprint Planning/Product Backlog - SOEN 341.xlsx
+++ b/Sprint Planning/Product Backlog - SOEN 341.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gagne\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{17A570B8-68AF-4F08-8BE7-D07FFA264283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BF9703DF-2742-4BB7-AF0A-36E945CCA3E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" activeTab="1" xr2:uid="{9FF516DD-DD1A-4540-862E-5B2452513E79}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{9FF516DD-DD1A-4540-862E-5B2452513E79}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover Page" sheetId="1" r:id="rId1"/>
     <sheet name="Product Back Log" sheetId="2" r:id="rId2"/>
+    <sheet name="Contribution" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +38,31 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="63">
+  <si>
+    <t>The Cool Team</t>
+  </si>
+  <si>
+    <t>Team Members:</t>
+  </si>
+  <si>
+    <t>Marie Ella Cambay</t>
+  </si>
+  <si>
+    <t>Charles Dahan</t>
+  </si>
+  <si>
+    <t>Ilyess Diyane</t>
+  </si>
+  <si>
+    <t>Frederic Gagne</t>
+  </si>
+  <si>
+    <t>Pablo Hernandez</t>
+  </si>
+  <si>
+    <t>Quetin Malichecq-Laroche</t>
+  </si>
   <si>
     <t>Issue#</t>
   </si>
@@ -63,32 +88,202 @@
     <t>Due Date</t>
   </si>
   <si>
-    <t>TEAM NAME</t>
-  </si>
-  <si>
-    <t>Team Members:</t>
-  </si>
-  <si>
-    <t>Marie Ella Cambay</t>
-  </si>
-  <si>
-    <t>Charles Dahan</t>
-  </si>
-  <si>
-    <t>Frederic Gagne</t>
-  </si>
-  <si>
-    <t>Pablo Hernandez</t>
-  </si>
-  <si>
-    <t>Quetin Malichecq-Laroche</t>
+    <t>When opening the website, the user is introduced with a login page</t>
+  </si>
+  <si>
+    <t>- Setup Website
+- Design and implement a login page
+- Configure website to display login page as default
+- Validate user input on the login display</t>
+  </si>
+  <si>
+    <t>HIGH</t>
+  </si>
+  <si>
+    <t>LOW</t>
+  </si>
+  <si>
+    <t>-Frederic
+- Marie
+- Pablo</t>
+  </si>
+  <si>
+    <t>On the login page, the user has to have the option to either login, or create an account</t>
+  </si>
+  <si>
+    <t>- Provide an option to navigate to account creation
+- Design and implement an account registration page
+- Validate registration input</t>
+  </si>
+  <si>
+    <t>MEDIUM</t>
+  </si>
+  <si>
+    <t>The user's information is saved when registered</t>
+  </si>
+  <si>
+    <t>- Define required user information
+- Create database to store information
+- Store user data upon registration
+- Prevent duplicate account
+- Confirm account creation</t>
+  </si>
+  <si>
+    <t>-Quentin</t>
+  </si>
+  <si>
+    <t>The user is able to manage his profile, with information like diet preferences, and allergies</t>
+  </si>
+  <si>
+    <t>- Design interface for profile management
+- Display user's information and possibility to modify them
+- Store dietary preferences and allergy data
+- Validate the user's inputs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Marie
+- Charles
+</t>
+  </si>
+  <si>
+    <t>When loged in, the user is introduced to the menu page with a user friendly interface and the weekly meal schedule</t>
+  </si>
+  <si>
+    <t>- Design a user friendly main menu
+- Display buttons for features like profile management, calorie tracker, and recipe creator
+- Implement weekly meal schedule
+- Allow the user to remake the schedule
+- Ensure the schedule doesn't repeat meals
+- Ensure menu page is only accessible after login</t>
+  </si>
+  <si>
+    <t>- Charles
+- Quentin</t>
+  </si>
+  <si>
+    <t>The user can access a page allowing to manage recipes (add, delete, modify, etc.)</t>
+  </si>
+  <si>
+    <t>- Design profile management interface
+- Design table that stores and displays the user's recipes
+- Implement system to add recipes
+- Implement system to remove recipes
+- Implement system to edit recipes</t>
+  </si>
+  <si>
+    <t>- Frederic Gagne</t>
+  </si>
+  <si>
+    <t>The user can look and filter through his recipes</t>
+  </si>
+  <si>
+    <t>- Design a recipe list layout that shows the key information of each recipes
+- Add search feature
+- Add filter option</t>
+  </si>
+  <si>
+    <t>- Pablo</t>
+  </si>
+  <si>
+    <t>The user can access a page where a calorie tracker advises him on his calorie consumption</t>
+  </si>
+  <si>
+    <t>- Design calorie tracker interface
+- Display total daily calories of the meals
+- Allow user's to add or remove daily calories from either eating food not in the schedule or exercise
+- Provide simple feedback and encouragements</t>
+  </si>
+  <si>
+    <t>The user can give all ingridients he has, the app will return him with suggestions of recipes that are possible with those ingredients</t>
+  </si>
+  <si>
+    <t>- Design ingredient input interface
+- Allow user's to input valid ingredients
+- Use AI API to look for recipes based on ingredients and suggest them to the user
+- Allow users to add given recipes to their list</t>
+  </si>
+  <si>
+    <t>- Frederic Gagne
+- Pablo</t>
+  </si>
+  <si>
+    <t>The user will enjoy an easy to learn user interface with fast response</t>
+  </si>
+  <si>
+    <t>- Create consistent and easy to navigate layout
+- Improve responsivness by reducing unecessary page reloads
+- Test the website with many different use cases to ensure bug free environment</t>
+  </si>
+  <si>
+    <t>- Marie
+- Charles</t>
+  </si>
+  <si>
+    <t>The user can live comfortably knowing that his stored data is protected</t>
+  </si>
+  <si>
+    <t>- Ensure personnal information is stored correctly and securely
+- Restrict data access to people within the team only
+- Document which data is being used where and in what way (only necessary for user's personal information)</t>
+  </si>
+  <si>
+    <t>- Quentin</t>
+  </si>
+  <si>
+    <t>Total story points</t>
+  </si>
+  <si>
+    <t>Sprint 1</t>
+  </si>
+  <si>
+    <t>Sprint 2</t>
+  </si>
+  <si>
+    <t>Sprint 3</t>
+  </si>
+  <si>
+    <t>Sprint 4</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Time Spent (hours)</t>
+  </si>
+  <si>
+    <t>Contributions</t>
+  </si>
+  <si>
+    <t>Debugged and resolved database insert errors (users now correctly save in phpMyAdmin)
+Improved UI/UX styling for the login and profile pages
+Added a consistent top header (logo + app name) across pages for a cleaner layout</t>
+  </si>
+  <si>
+    <t>Helped Setup the Github page by creating the GitHub issues
+Display the user's  dietary preferences on the profile page
+Store the allergies and dietary preferences data
+Link the allergies/preferences to the user</t>
+  </si>
+  <si>
+    <t>Created the GitHub, and helped fill out the product backlog.
+Setup the login and registration page.
+Setup the main menu and the profile page.
+Added the allergies in the profile page.</t>
+  </si>
+  <si>
+    <t>Helped set up Github files, and fill product backlog. 
+Kept record of meeting minutes</t>
+  </si>
+  <si>
+    <t>found and setup the database and website host
+setup and debugged connectivity between website and database</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -106,14 +301,45 @@
     </font>
     <font>
       <b/>
-      <sz val="36"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -126,8 +352,68 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF99CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF5050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -193,32 +479,339 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="12" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -226,6 +819,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFF5050"/>
+      <color rgb="FFFF0000"/>
+      <color rgb="FFFF99CC"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -554,362 +1154,757 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{339C796F-B13B-45AB-8363-E9D107B15827}">
-  <dimension ref="F5:I13"/>
+  <dimension ref="F5:I14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="6" max="6" width="14.453125" customWidth="1"/>
-    <col min="7" max="7" width="13.36328125" customWidth="1"/>
+    <col min="7" max="7" width="13.453125" customWidth="1"/>
     <col min="8" max="8" width="14.1796875" customWidth="1"/>
     <col min="9" max="9" width="13.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="5" spans="6:9" x14ac:dyDescent="0.35">
-      <c r="F5" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
+      <c r="F5" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
     </row>
     <row r="6" spans="6:9" ht="27" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-    </row>
-    <row r="8" spans="6:9" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="F8" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-    </row>
-    <row r="9" spans="6:9" x14ac:dyDescent="0.35">
-      <c r="F9" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-    </row>
-    <row r="10" spans="6:9" x14ac:dyDescent="0.35">
-      <c r="F10" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-    </row>
-    <row r="11" spans="6:9" x14ac:dyDescent="0.35">
-      <c r="F11" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-    </row>
-    <row r="12" spans="6:9" x14ac:dyDescent="0.35">
-      <c r="F12" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-    </row>
-    <row r="13" spans="6:9" x14ac:dyDescent="0.35">
-      <c r="F13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="54"/>
+    </row>
+    <row r="7" spans="6:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F7" s="52"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52"/>
+    </row>
+    <row r="8" spans="6:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F8" s="55" t="s">
+        <v>1</v>
+      </c>
+      <c r="G8" s="55"/>
+      <c r="H8" s="55"/>
+      <c r="I8" s="55"/>
+    </row>
+    <row r="9" spans="6:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F9" s="53" t="s">
+        <v>2</v>
+      </c>
+      <c r="G9" s="53"/>
+      <c r="H9" s="53"/>
+      <c r="I9" s="53"/>
+    </row>
+    <row r="10" spans="6:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F10" s="53" t="s">
+        <v>3</v>
+      </c>
+      <c r="G10" s="53"/>
+      <c r="H10" s="53"/>
+      <c r="I10" s="53"/>
+    </row>
+    <row r="11" spans="6:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F11" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="G11" s="53"/>
+      <c r="H11" s="53"/>
+      <c r="I11" s="53"/>
+    </row>
+    <row r="12" spans="6:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F12" s="53" t="s">
+        <v>5</v>
+      </c>
+      <c r="G12" s="53"/>
+      <c r="H12" s="53"/>
+      <c r="I12" s="53"/>
+    </row>
+    <row r="13" spans="6:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F13" s="53" t="s">
+        <v>6</v>
+      </c>
+      <c r="G13" s="53"/>
+      <c r="H13" s="53"/>
+      <c r="I13" s="53"/>
+    </row>
+    <row r="14" spans="6:9" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="F14" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="G14" s="53"/>
+      <c r="H14" s="53"/>
+      <c r="I14" s="53"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="F13:I13"/>
+  <mergeCells count="8">
+    <mergeCell ref="F14:I14"/>
     <mergeCell ref="F5:I6"/>
     <mergeCell ref="F8:I8"/>
     <mergeCell ref="F9:I9"/>
     <mergeCell ref="F10:I10"/>
+    <mergeCell ref="F12:I12"/>
+    <mergeCell ref="F13:I13"/>
     <mergeCell ref="F11:I11"/>
-    <mergeCell ref="F12:I12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B250A03-63F3-4E15-8498-7F40E007876F}">
-  <dimension ref="A1:H20"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.1796875" customWidth="1"/>
-    <col min="2" max="2" width="19.6328125" customWidth="1"/>
-    <col min="3" max="3" width="33" customWidth="1"/>
-    <col min="4" max="4" width="26" customWidth="1"/>
+    <col min="2" max="2" width="41.1796875" customWidth="1"/>
+    <col min="3" max="3" width="49.54296875" customWidth="1"/>
+    <col min="4" max="4" width="31.54296875" customWidth="1"/>
     <col min="5" max="5" width="17.1796875" customWidth="1"/>
-    <col min="6" max="6" width="13.08984375" customWidth="1"/>
-    <col min="7" max="7" width="25.6328125" customWidth="1"/>
-    <col min="8" max="8" width="13.6328125" customWidth="1"/>
+    <col min="6" max="6" width="13.1796875" customWidth="1"/>
+    <col min="7" max="7" width="25.54296875" customWidth="1"/>
+    <col min="8" max="8" width="13.54296875" customWidth="1"/>
+    <col min="11" max="11" width="14.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="19" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="65.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="28">
+        <v>1</v>
+      </c>
+      <c r="B2" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="30" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="31">
+        <v>2</v>
+      </c>
+      <c r="E2" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="31" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" s="33">
+        <v>46059</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="34">
+        <v>2</v>
+      </c>
+      <c r="B3" s="35" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="37">
+        <v>5</v>
+      </c>
+      <c r="E3" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="37" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="38">
+        <v>46059</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="81.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="34">
+        <v>3</v>
+      </c>
+      <c r="B4" s="39" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="37">
+        <v>3</v>
+      </c>
+      <c r="E4" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="37" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="38">
+        <v>46059</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="90.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="34">
+        <v>4</v>
+      </c>
+      <c r="B5" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="36" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="37">
+        <v>4</v>
+      </c>
+      <c r="E5" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="37" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5" s="38">
+        <v>46059</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="120.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="17">
+        <v>5</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="20">
+        <v>6</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" s="21">
+        <v>46108</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="96.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="22">
+        <v>6</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="25">
+        <v>5</v>
+      </c>
+      <c r="E7" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" s="26">
+        <v>46080</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="79.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="22">
+        <v>7</v>
+      </c>
+      <c r="B8" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="25">
+        <v>3</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="G8" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="H8" s="26">
+        <v>46080</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="80.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="41">
+        <v>8</v>
+      </c>
+      <c r="B9" s="42" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="43" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="44">
+        <v>6</v>
+      </c>
+      <c r="E9" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" s="44" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" s="43" t="s">
+        <v>32</v>
+      </c>
+      <c r="H9" s="45">
+        <v>46126</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="82.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="41">
+        <v>9</v>
+      </c>
+      <c r="B10" s="42" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" s="44">
+        <v>7</v>
+      </c>
+      <c r="E10" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" s="44" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="H10" s="45">
+        <v>46126</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="79.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="41">
+        <v>10</v>
+      </c>
+      <c r="B11" s="42" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="43" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" s="44">
+        <v>2</v>
+      </c>
+      <c r="E11" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="G11" s="43" t="s">
+        <v>46</v>
+      </c>
+      <c r="H11" s="45">
+        <v>46126</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="73" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="46">
+        <v>11</v>
+      </c>
+      <c r="B12" s="47" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="48" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="49">
+        <v>3</v>
+      </c>
+      <c r="E12" s="49" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" s="49" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="50" t="s">
+        <v>49</v>
+      </c>
+      <c r="H12" s="51">
+        <v>46126</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="56" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="57"/>
+      <c r="C13" s="58"/>
+      <c r="D13" s="5">
+        <f>SUM(D2:D12)</f>
+        <v>46</v>
+      </c>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" s="2"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" s="2"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" s="2"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17" s="2"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18" s="2"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A19" s="2"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A20" s="2"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A21" s="2"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A13:C13"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5036C424-2850-4E09-8C65-20F5EB166CA4}">
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="38.1796875" customWidth="1"/>
+    <col min="2" max="2" width="31.54296875" customWidth="1"/>
+    <col min="3" max="3" width="53.54296875" customWidth="1"/>
+    <col min="4" max="4" width="48.7265625" customWidth="1"/>
+    <col min="5" max="5" width="47.7265625" customWidth="1"/>
+    <col min="6" max="6" width="62.81640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="2" spans="1:7" ht="21.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C2" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="61" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" s="14">
+        <v>6</v>
+      </c>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="11">
+        <f>SUM(C3:F3)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="97.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="62"/>
+      <c r="B4" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="12"/>
+    </row>
+    <row r="5" spans="1:7" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="63" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" s="14">
+        <v>8</v>
+      </c>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="11">
+        <f>SUM(C5:F5)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="66.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="64"/>
+      <c r="B6" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="12"/>
+    </row>
+    <row r="7" spans="1:7" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="65" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="14">
+        <v>10</v>
+      </c>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="11">
+        <f>SUM(C7:F7)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="66.650000000000006" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="66"/>
+      <c r="B8" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="12"/>
+    </row>
+    <row r="9" spans="1:7" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="67" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="14">
+        <v>2</v>
+      </c>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="11">
+        <f>SUM(C9:F9)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="68"/>
+      <c r="B10" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="12"/>
+    </row>
+    <row r="11" spans="1:7" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="69" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="16">
+        <v>5</v>
+      </c>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="11">
+        <f>SUM(C11:F11)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="52.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="70"/>
+      <c r="B12" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="13"/>
+    </row>
+    <row r="13" spans="1:7" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="59" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="11">
+        <f>SUM(C13:F13)</f>
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" s="3">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" s="3">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" s="3">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" s="3">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" s="3">
-        <v>6</v>
-      </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" s="3">
-        <v>7</v>
-      </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A9" s="3">
-        <v>8</v>
-      </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" s="3">
-        <v>9</v>
-      </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11" s="3">
-        <v>10</v>
-      </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12" s="3">
-        <v>11</v>
-      </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" s="3">
-        <v>12</v>
-      </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A14" s="3">
-        <v>13</v>
-      </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A15" s="3">
-        <v>14</v>
-      </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A16" s="3">
-        <v>15</v>
-      </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A17" s="3">
-        <v>16</v>
-      </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A18" s="3">
-        <v>17</v>
-      </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A19" s="3">
-        <v>18</v>
-      </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-    </row>
-    <row r="20" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="4">
-        <v>19</v>
-      </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
+    </row>
+    <row r="14" spans="1:7" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="60"/>
+      <c r="B14" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="13"/>
     </row>
   </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A11:A12"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>